--- a/data/trans_orig/VUL_MENTALCOM-Clase-trans_orig.xlsx
+++ b/data/trans_orig/VUL_MENTALCOM-Clase-trans_orig.xlsx
@@ -651,8 +651,10 @@
           <t>Grupo I y II</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C4" s="4" t="n">
         <v>18</v>
@@ -720,8 +722,10 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" s="2" t="n">
-        <v>0</v>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C5" s="4" t="n">
         <v>360</v>
@@ -864,8 +868,10 @@
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>1</v>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C7" s="4" t="n">
         <v>19</v>
@@ -933,8 +939,10 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
-      <c r="B8" s="2" t="n">
-        <v>0</v>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>283</v>
@@ -1077,8 +1085,10 @@
           <t>Grupo IV y V</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>1</v>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C10" s="4" t="n">
         <v>17</v>
@@ -1146,8 +1156,10 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
-      <c r="B11" s="2" t="n">
-        <v>0</v>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C11" s="4" t="n">
         <v>212</v>
@@ -1290,8 +1302,10 @@
           <t>Grupo VI</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>1</v>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C13" s="4" t="n">
         <v>35</v>
@@ -1359,8 +1373,10 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
-      <c r="B14" s="2" t="n">
-        <v>0</v>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C14" s="4" t="n">
         <v>446</v>
@@ -1503,8 +1519,10 @@
           <t>Grupo VII</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>1</v>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C16" s="4" t="n">
         <v>13</v>
@@ -1572,8 +1590,10 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
-      <c r="B17" s="2" t="n">
-        <v>0</v>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C17" s="4" t="n">
         <v>162</v>
@@ -1716,8 +1736,10 @@
           <t>No ha trabajado</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
-        <v>1</v>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C19" s="4" t="n">
         <v>8</v>
@@ -1785,8 +1807,10 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n"/>
-      <c r="B20" s="2" t="n">
-        <v>0</v>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C20" s="4" t="n">
         <v>60</v>
@@ -1929,8 +1953,10 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
-        <v>1</v>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C22" s="4" t="n">
         <v>110</v>
@@ -1998,8 +2024,10 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
-      <c r="B23" s="2" t="n">
-        <v>0</v>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C23" s="4" t="n">
         <v>1523</v>
@@ -2376,8 +2404,10 @@
           <t>Grupo I y II</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C4" s="4" t="n">
         <v>70</v>
@@ -2445,8 +2475,10 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" s="2" t="n">
-        <v>0</v>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C5" s="4" t="n">
         <v>531</v>
@@ -2589,8 +2621,10 @@
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>1</v>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C7" s="4" t="n">
         <v>51</v>
@@ -2658,8 +2692,10 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
-      <c r="B8" s="2" t="n">
-        <v>0</v>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>249</v>
@@ -2802,8 +2838,10 @@
           <t>Grupo IV y V</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>1</v>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C10" s="4" t="n">
         <v>45</v>
@@ -2871,8 +2909,10 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
-      <c r="B11" s="2" t="n">
-        <v>0</v>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C11" s="4" t="n">
         <v>162</v>
@@ -3015,8 +3055,10 @@
           <t>Grupo VI</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>1</v>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C13" s="4" t="n">
         <v>71</v>
@@ -3084,8 +3126,10 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
-      <c r="B14" s="2" t="n">
-        <v>0</v>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C14" s="4" t="n">
         <v>264</v>
@@ -3228,8 +3272,10 @@
           <t>Grupo VII</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>1</v>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C16" s="4" t="n">
         <v>13</v>
@@ -3297,8 +3343,10 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
-      <c r="B17" s="2" t="n">
-        <v>0</v>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C17" s="4" t="n">
         <v>89</v>
@@ -3441,8 +3489,10 @@
           <t>No ha trabajado</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
-        <v>1</v>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C19" s="4" t="n">
         <v>10</v>
@@ -3510,8 +3560,10 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n"/>
-      <c r="B20" s="2" t="n">
-        <v>0</v>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C20" s="4" t="n">
         <v>80</v>
@@ -3654,8 +3706,10 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
-        <v>1</v>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C22" s="4" t="n">
         <v>260</v>
@@ -3723,8 +3777,10 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
-      <c r="B23" s="2" t="n">
-        <v>0</v>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C23" s="4" t="n">
         <v>1375</v>
@@ -4101,8 +4157,10 @@
           <t>Grupo I y II</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C4" s="4" t="n">
         <v>9</v>
@@ -4170,8 +4228,10 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" s="2" t="n">
-        <v>0</v>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C5" s="4" t="n">
         <v>442</v>
@@ -4314,8 +4374,10 @@
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>1</v>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C7" s="4" t="n">
         <v>12</v>
@@ -4383,8 +4445,10 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
-      <c r="B8" s="2" t="n">
-        <v>0</v>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>277</v>
@@ -4527,8 +4591,10 @@
           <t>Grupo IV y V</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>1</v>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C10" s="4" t="n">
         <v>11</v>
@@ -4596,8 +4662,10 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
-      <c r="B11" s="2" t="n">
-        <v>0</v>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C11" s="4" t="n">
         <v>268</v>
@@ -4740,8 +4808,10 @@
           <t>Grupo VI</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>1</v>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C13" s="4" t="n">
         <v>12</v>
@@ -4809,8 +4879,10 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
-      <c r="B14" s="2" t="n">
-        <v>0</v>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C14" s="4" t="n">
         <v>447</v>
@@ -4953,8 +5025,10 @@
           <t>Grupo VII</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>1</v>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C16" s="4" t="n">
         <v>10</v>
@@ -5022,8 +5096,10 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
-      <c r="B17" s="2" t="n">
-        <v>0</v>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C17" s="4" t="n">
         <v>186</v>
@@ -5166,8 +5242,10 @@
           <t>No ha trabajado</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
-        <v>1</v>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C19" s="4" t="n">
         <v>0</v>
@@ -5227,8 +5305,10 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n"/>
-      <c r="B20" s="2" t="n">
-        <v>0</v>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C20" s="4" t="n">
         <v>11</v>
@@ -5363,8 +5443,10 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
-        <v>1</v>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C22" s="4" t="n">
         <v>54</v>
@@ -5432,8 +5514,10 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
-      <c r="B23" s="2" t="n">
-        <v>0</v>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C23" s="4" t="n">
         <v>1631</v>
@@ -5810,8 +5894,10 @@
           <t>Grupo I y II</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C4" s="4" t="n">
         <v>26</v>
@@ -5879,8 +5965,10 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" s="2" t="n">
-        <v>0</v>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C5" s="4" t="n">
         <v>723</v>
@@ -6023,8 +6111,10 @@
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>1</v>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C7" s="4" t="n">
         <v>16</v>
@@ -6092,8 +6182,10 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
-      <c r="B8" s="2" t="n">
-        <v>0</v>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>417</v>
@@ -6236,8 +6328,10 @@
           <t>Grupo IV y V</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>1</v>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C10" s="4" t="n">
         <v>35</v>
@@ -6305,8 +6399,10 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
-      <c r="B11" s="2" t="n">
-        <v>0</v>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C11" s="4" t="n">
         <v>749</v>
@@ -6449,8 +6545,10 @@
           <t>Grupo VI</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>1</v>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C13" s="4" t="n">
         <v>47</v>
@@ -6518,8 +6616,10 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
-      <c r="B14" s="2" t="n">
-        <v>0</v>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C14" s="4" t="n">
         <v>828</v>
@@ -6662,8 +6762,10 @@
           <t>Grupo VII</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>1</v>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C16" s="4" t="n">
         <v>8</v>
@@ -6731,8 +6833,10 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
-      <c r="B17" s="2" t="n">
-        <v>0</v>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C17" s="4" t="n">
         <v>355</v>
@@ -6875,8 +6979,10 @@
           <t>No ha trabajado</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
-        <v>1</v>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C19" s="4" t="n">
         <v>4</v>
@@ -6944,8 +7050,10 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n"/>
-      <c r="B20" s="2" t="n">
-        <v>0</v>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C20" s="4" t="n">
         <v>221</v>
@@ -7088,8 +7196,10 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
-        <v>1</v>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C22" s="4" t="n">
         <v>136</v>
@@ -7157,8 +7267,10 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
-      <c r="B23" s="2" t="n">
-        <v>0</v>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C23" s="4" t="n">
         <v>3293</v>
